--- a/data/reference/kesser_master_account_mapping.xlsx
+++ b/data/reference/kesser_master_account_mapping.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>Other Income / Expense</t>
+          <t>Other Operating Revenue</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>Other Income / Expense</t>
+          <t>Other Operating Revenue</t>
         </is>
       </c>
       <c r="E47" s="17" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D49" s="17" t="inlineStr">
         <is>
-          <t>Other Income / Expense</t>
+          <t>Other Operating Revenue</t>
         </is>
       </c>
       <c r="E49" s="17" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="D214" s="17" t="inlineStr">
         <is>
-          <t>Other Income / Expense</t>
+          <t>Other Operating Revenue</t>
         </is>
       </c>
       <c r="E214" s="17" t="inlineStr">
